--- a/lessons/qr/excels/remarks_lcs.xlsx
+++ b/lessons/qr/excels/remarks_lcs.xlsx
@@ -2522,6 +2522,11 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +CANCEL (00:00:00), +SCAN (00:00:00), +btn (00:00:00), +btn (00:00:00), +innerText (00:00:00), +innerText (00:00:00), +sqrcode (00:00:00), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -qrcode (13:05:55.667), -; (13:11:40.424)</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="M30" t="n">
         <v>99.09999999999999</v>
       </c>
@@ -2595,7 +2600,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Q, Q</t>
+          <t>Q, Q, H</t>
         </is>
       </c>
       <c r="M31" t="n">
